--- a/四均線起漲圖表_20260611/四均線起漲精選_20260611.xlsx
+++ b/四均線起漲圖表_20260611/四均線起漲精選_20260611.xlsx
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -118,6 +118,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -542,32 +557,134 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6156.TWO</t>
+          <t>6186.TWO</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>松上</t>
+          <t>新潤</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>20.45</v>
+        <v>42</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>4374</v>
+        <v>3498</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1339</v>
+        <v>1640</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>5534.TW</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>長虹</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>3.08%</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>7305</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>3428</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2537.TW</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>聯上發</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>3.59%</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9520</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2960</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>9940.TW</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>信義</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>3.71%</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>2242</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>1008</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -576,6 +693,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
